--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488131_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488131_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5534</v>
+        <v>5.8416</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5461</v>
+        <v>7.1544</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9927</v>
+        <v>-1.3128</v>
       </c>
       <c r="G2" t="n">
         <v>6.9999</v>
@@ -610,13 +610,13 @@
         <v>3.7057</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4979</v>
+        <v>-0.2139</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0284</v>
+        <v>0.6367</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5305</v>
+        <v>-0.8506</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9444</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6056</v>
+        <v>4.464</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3382</v>
+        <v>3.9257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2675</v>
+        <v>0.5383</v>
       </c>
       <c r="G3" t="n">
         <v>4.2406</v>
@@ -688,13 +688,13 @@
         <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8029</v>
+        <v>-0.9445</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5471</v>
+        <v>0.0404</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2557</v>
+        <v>-0.9849</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.623</v>
+        <v>2.1883</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4125</v>
+        <v>2.1883</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2105</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4034</v>
+        <v>2.1883</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7782</v>
+        <v>0.3221</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6252</v>
+        <v>1.8662</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6292</v>
+        <v>2.1883</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2192</v>
+        <v>0.3221</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.8662</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2258</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.441</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2152</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1499</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4785</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1926</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7141</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6039</v>
+        <v>1.7898</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4585</v>
+        <v>-0.273</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1454</v>
+        <v>2.0628</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0192</v>
+        <v>2.4034</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2849</v>
+        <v>0.7782</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2657</v>
+        <v>1.6252</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3753</v>
+        <v>2.6292</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8931</v>
+        <v>1.2192</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5178</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3945</v>
+        <v>-0.2258</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.178</v>
+        <v>-0.441</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7834</v>
+        <v>0.2152</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4087</v>
+        <v>3.1499</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1408</v>
+        <v>-0.3547</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0096</v>
+        <v>0.5071</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8687</v>
+        <v>-0.8618</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1883</v>
+        <v>1.1842</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1883</v>
+        <v>-0.0105</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.1947</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1883</v>
+        <v>-0.0192</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3221</v>
+        <v>-0.2849</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8662</v>
+        <v>0.2657</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1883</v>
+        <v>0.3753</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3221</v>
+        <v>0.8931</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8662</v>
+        <v>-0.5178</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.3945</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.178</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.2789</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.5406</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.8195</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.733</v>
+        <v>-0.4376</v>
       </c>
       <c r="E7" t="n">
         <v>-2.0316</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2986</v>
+        <v>1.594</v>
       </c>
       <c r="G7" t="n">
         <v>0.6172</v>
@@ -1000,13 +1000,13 @@
         <v>2.7793</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7207</v>
+        <v>-0.4253</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.717</v>
+        <v>-0.4216</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5007</v>
+        <v>-1.0597</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1928</v>
+        <v>-0.8011</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3079</v>
+        <v>-0.2586</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4241</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6325</v>
+        <v>-0.1915</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2736</v>
+        <v>0.1181</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3589</v>
+        <v>-0.3096</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6071</v>
+        <v>-1.0934</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0011</v>
+        <v>-2.4135</v>
       </c>
       <c r="F10" t="n">
-        <v>1.394</v>
+        <v>1.3201</v>
       </c>
       <c r="G10" t="n">
         <v>0.008999999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0602</v>
+        <v>-0.5465</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6566</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4037</v>
+        <v>-0.4775</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3587</v>
+        <v>-2.9423</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9783</v>
+        <v>-2.5866</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3804</v>
+        <v>-0.3558</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3875</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8976</v>
+        <v>-0.4813</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5471</v>
+        <v>-0.1554</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3504</v>
+        <v>-0.3258</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8208</v>
+        <v>-4.381</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.047</v>
+        <v>-3.4594</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7739</v>
+        <v>-0.9216</v>
       </c>
       <c r="G12" t="n">
         <v>-0.39</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3371</v>
+        <v>-0.8972</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4924</v>
+        <v>0.0951</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8446</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3144</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.782500000000001</v>
+        <v>4.782499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0814</v>
+        <v>1.081300000000001</v>
       </c>
       <c r="F13" t="n">
         <v>3.7011</v>
@@ -1447,7 +1447,7 @@
         <v>13.405</v>
       </c>
       <c r="L13" t="n">
-        <v>5.7199</v>
+        <v>5.719900000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-6.7132</v>
@@ -1468,13 +1468,13 @@
         <v>21.308</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.464399999999999</v>
+        <v>-4.4644</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7101</v>
+        <v>1.7099</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.174199999999999</v>
+        <v>-6.174300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0909</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0843</v>
+        <v>3.7866</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6318</v>
+        <v>2.3587</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4525</v>
+        <v>1.4279</v>
       </c>
       <c r="G14" t="n">
         <v>1.5628</v>
@@ -1546,13 +1546,13 @@
         <v>3.891</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7803</v>
+        <v>1.4826</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4983</v>
+        <v>1.2252</v>
       </c>
       <c r="U14" t="n">
-        <v>0.282</v>
+        <v>0.2574</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5632</v>
+        <v>2.6908</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4672</v>
+        <v>3.3486</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9039</v>
+        <v>-0.6577</v>
       </c>
       <c r="G15" t="n">
         <v>3.7195</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4152</v>
+        <v>-0.2876</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5471</v>
+        <v>0.3342</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.868</v>
+        <v>-0.6218</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3178</v>
+        <v>1.6614</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2295</v>
+        <v>-0.0336</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5472</v>
+        <v>1.695</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1632</v>
@@ -1702,13 +1702,13 @@
         <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0548</v>
+        <v>1.3984</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8133</v>
+        <v>1.0091</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2415</v>
+        <v>0.3892</v>
       </c>
       <c r="V16" t="n">
         <v>0.3144</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7291</v>
+        <v>0.3069</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5167</v>
+        <v>0.3663</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7876</v>
+        <v>-0.0593</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3365</v>
+        <v>0.0329</v>
       </c>
       <c r="H18" t="n">
-        <v>1.496</v>
+        <v>0.9929</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1596</v>
+        <v>-0.96</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1333</v>
+        <v>0.3778</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7861</v>
+        <v>1.0306</v>
       </c>
       <c r="L18" t="n">
         <v>-0.6529</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7968</v>
+        <v>-0.3448</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2901</v>
+        <v>-0.0377</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5067</v>
+        <v>-0.3071</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.297</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4308</v>
+        <v>-0.5413</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9774</v>
+        <v>-0.0115</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5467</v>
+        <v>-0.5298</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2589</v>
+        <v>0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.599</v>
+        <v>0.2635</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4043</v>
+        <v>1.125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1947</v>
+        <v>-0.8615</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8417</v>
+        <v>0.3365</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2289</v>
+        <v>1.496</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3872</v>
+        <v>-1.1596</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6467</v>
+        <v>1.1333</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6882</v>
+        <v>1.7861</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0415</v>
+        <v>-0.6529</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.195</v>
+        <v>-0.7968</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5407</v>
+        <v>-0.2901</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3457</v>
+        <v>-0.5067</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4823</v>
+        <v>-1.297</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>1.014</v>
+        <v>-0.0348</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9774</v>
+        <v>0.5857</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0365</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9444</v>
+        <v>1.2589</v>
       </c>
       <c r="W19" t="n">
         <v>1.2589</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1351</v>
+        <v>0.0103</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2683</v>
+        <v>0.0126</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1332</v>
+        <v>-0.0023</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0329</v>
+        <v>-2.8417</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9929</v>
+        <v>-3.2289</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.96</v>
+        <v>0.3872</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3778</v>
+        <v>-1.6467</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0306</v>
+        <v>-1.6882</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6529</v>
+        <v>0.0415</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3448</v>
+        <v>-1.195</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0377</v>
+        <v>-1.5407</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3071</v>
+        <v>0.3457</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1853</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.713</v>
+        <v>0.4253</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1094</v>
+        <v>0.5857</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6036</v>
+        <v>-0.1604</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>0.9444</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X20" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4831</v>
+        <v>-0.3433</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4233</v>
+        <v>0.0401</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0598</v>
+        <v>-0.3834</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5847</v>
+        <v>0.2483</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1518</v>
+        <v>0.6906</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4329</v>
+        <v>-0.4422</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1947</v>
+        <v>1.5357</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6663</v>
+        <v>1.4943</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5284</v>
+        <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.39</v>
+        <v>-1.2874</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4855</v>
+        <v>-0.8037</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9044</v>
+        <v>-0.4837</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1499</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7793</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2133</v>
+        <v>0.1495</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6624</v>
+        <v>0.3572</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.2077</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0534</v>
+        <v>-1.6786</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6454</v>
+        <v>-1.4795</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.408</v>
+        <v>-0.1991</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2483</v>
+        <v>-2.1447</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6906</v>
+        <v>-0.5043</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4422</v>
+        <v>-1.6404</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5357</v>
+        <v>-0.135</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4943</v>
+        <v>0.4764</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2874</v>
+        <v>-2.0097</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8037</v>
+        <v>-0.9807</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4837</v>
+        <v>-1.029</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5606</v>
+        <v>0.6519</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3283</v>
+        <v>0.5089</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2323</v>
+        <v>0.143</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9724</v>
+        <v>-1.9045</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7733</v>
+        <v>-1.5985</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1991</v>
+        <v>-0.306</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1447</v>
+        <v>-4.5847</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5043</v>
+        <v>-2.1518</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6404</v>
+        <v>-2.4329</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.135</v>
+        <v>-1.1947</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4764</v>
+        <v>-0.6663</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5284</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0097</v>
+        <v>-3.39</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9807</v>
+        <v>-1.4855</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.029</v>
+        <v>-1.9044</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>-3.1499</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6676</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3581</v>
+        <v>1.7919</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2151</v>
+        <v>1.4873</v>
       </c>
       <c r="U23" t="n">
-        <v>0.143</v>
+        <v>0.3046</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0005</v>
+        <v>1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0005</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5304</v>
+        <v>-5.114</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9583</v>
+        <v>-3.5666</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5721</v>
+        <v>-1.5475</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7845</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7459</v>
+        <v>-0.3295</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.383</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3629</v>
+        <v>-0.3383</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6294</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.116</v>
+        <v>-5.4058</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9038</v>
+        <v>-5.2183</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2121</v>
+        <v>-0.1875</v>
       </c>
       <c r="G25" t="n">
         <v>-4.7369</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9523</v>
+        <v>-0.2422</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6019</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3504</v>
+        <v>-0.3258</v>
       </c>
       <c r="V25" t="n">
         <v>0.3144</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7827</v>
+        <v>-4.782600000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.701200000000001</v>
+        <v>-3.7011</v>
       </c>
       <c r="F26" t="n">
         <v>-1.0814</v>
@@ -2458,7 +2458,7 @@
         <v>6.713300000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>8.326899999999998</v>
+        <v>8.3269</v>
       </c>
       <c r="L26" t="n">
         <v>-1.6137</v>
@@ -2482,16 +2482,16 @@
         <v>20.3815</v>
       </c>
       <c r="S26" t="n">
-        <v>4.464300000000001</v>
+        <v>4.464199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>6.1742</v>
+        <v>6.1741</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.71</v>
+        <v>-1.7101</v>
       </c>
       <c r="V26" t="n">
-        <v>4.091100000000001</v>
+        <v>4.091099999999999</v>
       </c>
       <c r="W26" t="n">
         <v>4.7195</v>
